--- a/GeoMIP/results/resultados_todos_csv.xlsx
+++ b/GeoMIP/results/resultados_todos_csv.xlsx
@@ -509,15 +509,15 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009906291961669922</v>
+        <v>0.1238033771514893</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004967451095581055</v>
+        <v>0.1301727294921875</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>| ∅ || A |
-| b || ∅ |</t>
+          <t>| B || A |
+| a || b |</t>
         </is>
       </c>
     </row>
@@ -557,15 +557,15 @@
         <v>0.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001716852188110352</v>
+        <v>0.1280970573425293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006204366683959961</v>
+        <v>0.2751545906066895</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>|   ∅   || A,C |
-| a,b,c ||  ∅  |</t>
+          <t>|  A,C  || B |
+| a,b,c || ∅ |</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002071619033813477</v>
+        <v>0.2696342468261719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006204366683959961</v>
+        <v>0.2751545906066895</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>|   ∅   || A,B,C || ∅ |
-| a,b,c ||   ∅   || ∅ |</t>
+          <t>| ∅ || A,B || C |
+| a || b,c || ∅ |</t>
         </is>
       </c>
     </row>
@@ -653,15 +653,15 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001389503479003906</v>
+        <v>0.1285502910614014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005249500274658203</v>
+        <v>0.2908322811126709</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>|  ∅  || A,B,C |
-| a,c ||   ∅   |</t>
+          <t>|  A  || B,C |
+| a,b ||  c  |</t>
         </is>
       </c>
     </row>
@@ -698,18 +698,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001679897308349609</v>
+        <v>0.2846944332122803</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005249500274658203</v>
+        <v>0.2908322811126709</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>|   ∅   || A,B,C || ∅ |
-| a,b,c ||   ∅   || ∅ |</t>
+          <t>| A || ∅ || B,C |
+| a || b ||  c  |</t>
         </is>
       </c>
     </row>
@@ -749,15 +749,15 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001423835754394531</v>
+        <v>0.1397707462310791</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005321264266967773</v>
+        <v>0.3371376991271973</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>|  ∅  || A,B |
-| b,c ||  ∅  |</t>
+          <t>| A,C || B |
+| a,c || b |</t>
         </is>
       </c>
     </row>
@@ -794,18 +794,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001702785491943359</v>
+        <v>0.3257012367248535</v>
       </c>
       <c r="J8" t="n">
-        <v>0.005321264266967773</v>
+        <v>0.3371376991271973</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>|   ∅   || A,B,C || ∅ |
-| a,b,c ||   ∅   || ∅ |</t>
+          <t>| C || B || A |
+| a || b || c |</t>
         </is>
       </c>
     </row>
@@ -845,15 +845,15 @@
         <v>0.25</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002791643142700195</v>
+        <v>0.1933979988098145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01007580757141113</v>
+        <v>1.007938146591187</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>|    ∅    || A,C,D |
-| a,b,c,d ||   ∅   |</t>
+          <t>|  A,C,D  || B |
+| a,b,c,d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -890,18 +890,18 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00422978401184082</v>
+        <v>0.5425980091094971</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01007580757141113</v>
+        <v>1.007938146591187</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ |
-| a,b,c,d ||    ∅    || ∅ |</t>
+          <t>| ∅ || A,B,D || C |
+| a || b,c,d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -938,18 +938,18 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.25</v>
+        <v>0.875</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004669666290283203</v>
+        <v>0.9986369609832764</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01007580757141113</v>
+        <v>1.007938146591187</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ || ∅ |
-| a,b,c,d ||    ∅    || ∅ || ∅ |</t>
+          <t>|  C  || B || D || A |
+| a,b || c || d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -989,15 +989,15 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002469778060913086</v>
+        <v>0.1626307964324951</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009653091430664062</v>
+        <v>0.7125263214111328</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>|   ∅   || A,B,C,D |
-| b,c,d ||    ∅    |</t>
+          <t>| A,C,D || B |
+| a,b,c || d |</t>
         </is>
       </c>
     </row>
@@ -1034,18 +1034,18 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3499999642372131</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.004108190536499023</v>
+        <v>0.4168679714202881</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009653091430664062</v>
+        <v>0.7125263214111328</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ |
-| a,b,c,d ||    ∅    || ∅ |</t>
+          <t>| ∅ || A,B,C,D || ∅ |
+| a ||   b,d   || c |</t>
         </is>
       </c>
     </row>
@@ -1082,18 +1082,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.5249999761581421</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.004509687423706055</v>
+        <v>0.7018773555755615</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009653091430664062</v>
+        <v>0.7125263214111328</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ || ∅ |
-| a,b,c,d ||    ∅    || ∅ || ∅ |</t>
+          <t>| ∅ || C,D || ∅ || A,B |
+| a ||  b  || c ||  d  |</t>
         </is>
       </c>
     </row>
@@ -1133,15 +1133,15 @@
         <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00400233268737793</v>
+        <v>0.1826109886169434</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01107120513916016</v>
+        <v>0.7982993125915527</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,D |
-| a,b,c,d ||   ∅   |</t>
+          <t>|  A,B,D  || C |
+| a,b,c,d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1181,15 +1181,15 @@
         <v>0.625</v>
       </c>
       <c r="I16" t="n">
-        <v>0.005311965942382812</v>
+        <v>0.4307644367218018</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01107120513916016</v>
+        <v>0.7982993125915527</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ |
-| a,b,c,d ||    ∅    || ∅ |</t>
+          <t>| A,B,D || ∅ || C |
+| a,c,d || b || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1226,18 +1226,18 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005678892135620117</v>
+        <v>0.780515193939209</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01107120513916016</v>
+        <v>0.7982993125915527</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,C,D || ∅ || ∅ |
-| a,b,c,d ||    ∅    || ∅ || ∅ |</t>
+          <t>| B,D || A || ∅ || C |
+| a,c || b || d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1277,15 +1277,15 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005136013031005859</v>
+        <v>0.2542464733123779</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01832056045532227</v>
+        <v>2.147923946380615</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,E |
-| a,b,c,d,e ||    ∅    |</t>
+          <t>| A,B,C,D,E || ∅ |
+|  a,b,c,d  || e |</t>
         </is>
       </c>
     </row>
@@ -1322,18 +1322,18 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.009548425674438477</v>
+        <v>0.6344494819641113</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01832056045532227</v>
+        <v>2.147923946380615</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ |</t>
+          <t>| A,B,C,E || ∅ || D |
+| a,b,c,d || e || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1370,18 +1370,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0120384693145752</v>
+        <v>1.394957304000854</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01832056045532227</v>
+        <v>2.147923946380615</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ || ∅ |</t>
+          <t>|  A,C,E  || ∅ || B || D |
+| a,b,c,d || e || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1418,18 +1418,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01275181770324707</v>
+        <v>2.11639666557312</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01832056045532227</v>
+        <v>2.147923946380615</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ || ∅ || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ || ∅ || ∅ |</t>
+          <t>| ∅ || A,B,E || ∅ || C || D |
+| a || b,c,d || e || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1469,15 +1469,15 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004069328308105469</v>
+        <v>0.2619740962982178</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01677155494689941</v>
+        <v>1.902477025985718</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>|    ∅    || A,B,D,E |
-| b,c,d,e ||    ∅    |</t>
+          <t>| C || A,B,D,E |
+| a || b,c,d,e |</t>
         </is>
       </c>
     </row>
@@ -1514,18 +1514,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="I23" t="n">
-        <v>0.007253646850585938</v>
+        <v>0.6396253108978271</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01677155494689941</v>
+        <v>1.902477025985718</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ |</t>
+          <t>| C ||  A,B,D  || E |
+| a || b,c,d,e || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1562,18 +1562,18 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.009698867797851562</v>
+        <v>1.194270133972168</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01677155494689941</v>
+        <v>1.902477025985718</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ || ∅ |</t>
+          <t>| C || A,D,E || ∅ || B |
+| a || b,c,e || d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1610,18 +1610,18 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.75</v>
+        <v>0.875</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01063156127929688</v>
+        <v>1.819049596786499</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01677155494689941</v>
+        <v>1.902477025985718</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>|     ∅     || A,B,C,D,E || ∅ || ∅ || ∅ |
-| a,b,c,d,e ||     ∅     || ∅ || ∅ || ∅ |</t>
+          <t>| ∅ || ∅ || A,B,D || C || E |
+| a || b || c,d,e || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1661,15 +1661,15 @@
         <v>0.4375</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00743556022644043</v>
+        <v>0.3510770797729492</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03334188461303711</v>
+        <v>3.356868505477905</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>|      ∅      || A,B,C,E,F |
-| a,b,c,d,e,f ||     ∅     |</t>
+          <t>|  A,B,C,E,F  || D |
+| a,b,c,d,e,f || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1706,18 +1706,18 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.90625</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01485371589660645</v>
+        <v>1.255131244659424</v>
       </c>
       <c r="J27" t="n">
-        <v>0.03334188461303711</v>
+        <v>3.356868505477905</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>|      ∅      || A,B,C,D,E,F || ∅ |
-| a,b,c,d,e,f ||      ∅      || ∅ |</t>
+          <t>|   A,B,C,F   || D || E |
+| a,b,c,d,e,f || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1754,18 +1754,18 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.4375</v>
+        <v>1.15625</v>
       </c>
       <c r="I28" t="n">
-        <v>0.02282142639160156</v>
+        <v>2.270017862319946</v>
       </c>
       <c r="J28" t="n">
-        <v>0.03334188461303711</v>
+        <v>3.356868505477905</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>|      ∅      || A,B,C,D,E,F || ∅ || ∅ |
-| a,b,c,d,e,f ||      ∅      || ∅ || ∅ |</t>
+          <t>|  A,C,D,E  || ∅ || B || F |
+| a,b,c,d,e || f || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1802,18 +1802,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.921875</v>
+        <v>1.8125</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02640390396118164</v>
+        <v>3.257100820541382</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03334188461303711</v>
+        <v>3.356868505477905</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>|      ∅      || A,B,C,D,E,F || ∅ || ∅ || ∅ |
-| a,b,c,d,e,f ||      ∅      || ∅ || ∅ || ∅ |</t>
+          <t>|   E,F   ||  B  || A || C || D |
+| a,c,d,f || b,e || ∅ || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -1853,15 +1853,15 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02145934104919434</v>
+        <v>0.5202281475067139</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1142504215240479</v>
+        <v>4.837799072265625</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>|       ∅       || A,B,C,D,E,F,G |
-| b,c,d,e,f,g,h ||       ∅       |</t>
+          <t>| A,B,D,E,F,G,H || C |
+| a,b,c,d,e,g,h || f |</t>
         </is>
       </c>
     </row>
@@ -1898,18 +1898,18 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.04403352737426758</v>
+        <v>1.523412466049194</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1142504215240479</v>
+        <v>4.837799072265625</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>|        ∅        || A,B,C,D,E,F,G,H || ∅ |
-| a,b,c,d,e,f,g,h ||        ∅        || ∅ |</t>
+          <t>| H || B,C,D,E,G || A,F |
+| a || b,d,e,f,g || c,h |</t>
         </is>
       </c>
     </row>
@@ -1946,18 +1946,18 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07718467712402344</v>
+        <v>3.27008843421936</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1142504215240479</v>
+        <v>4.837799072265625</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>|        ∅        || A,B,C,D,E,F,G,H || ∅ || ∅ |
-| a,b,c,d,e,f,g,h ||        ∅        || ∅ || ∅ |</t>
+          <t>| A,E,G,H || B,F || D || C |
+| a,b,d,h || c,g || e || f |</t>
         </is>
       </c>
     </row>
@@ -1994,18 +1994,18 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.107792854309082</v>
+        <v>4.642372608184814</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1142504215240479</v>
+        <v>4.837799072265625</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>|        ∅        || A,B,C,D,E,F,G,H || ∅ || ∅ || ∅ |
-| a,b,c,d,e,f,g,h ||        ∅        || ∅ || ∅ || ∅ |</t>
+          <t>| H || G || F || A,B,D,E || C |
+| a || b || c || d,e,g,h || f |</t>
         </is>
       </c>
     </row>
@@ -2045,15 +2045,15 @@
         <v>0.47265625</v>
       </c>
       <c r="I34" t="n">
-        <v>0.06672143936157227</v>
+        <v>0.8416051864624023</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5110301971435547</v>
+        <v>8.985269069671631</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>|          ∅          || A,B,C,D,E,F,G,H,J |
-| a,b,c,d,e,f,g,h,i,j ||         ∅         |</t>
+          <t>|  A,B,C,D,E,F,G,H,J  || I |
+| a,b,c,d,e,f,g,h,i,j || ∅ |</t>
         </is>
       </c>
     </row>
@@ -2090,18 +2090,18 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.966796875</v>
+        <v>0.953125</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1022188663482666</v>
+        <v>2.888075828552246</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5110301971435547</v>
+        <v>8.985269069671631</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>|          ∅          || A,B,C,D,E,F,G,H,I,J || ∅ |
-| a,b,c,d,e,f,g,h,i,j ||          ∅          || ∅ |</t>
+          <t>|   A,B,D,E,F,G,H,J   || C || I |
+| a,b,c,d,e,f,g,h,i,j || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -2138,18 +2138,18 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.478515625</v>
+        <v>1.447265625</v>
       </c>
       <c r="I36" t="n">
-        <v>0.195704460144043</v>
+        <v>5.048506736755371</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5110301971435547</v>
+        <v>8.985269069671631</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>|          ∅          || A,B,C,D,E,F,G,H,I,J || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j ||          ∅          || ∅ || ∅ |</t>
+          <t>|    B,C,D,E,F,G,H    || A || I || J |
+| a,b,c,d,e,f,g,h,i,j || ∅ || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -2186,18 +2186,18 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.9736328125</v>
+        <v>1.9541015625</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5044844150543213</v>
+        <v>8.601722478866577</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5110301971435547</v>
+        <v>8.985269069671631</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>|          ∅          || A,B,C,D,E,F,G,H,I,J || ∅ || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j ||          ∅          || ∅ || ∅ || ∅ |</t>
+          <t>|     B,C,D,E,G,H     || A || F || I || J |
+| a,b,c,d,e,f,g,h,i,j || ∅ || ∅ || ∅ || ∅ |</t>
         </is>
       </c>
     </row>
@@ -2237,15 +2237,15 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>5.774192333221436</v>
+        <v>1.803292989730835</v>
       </c>
       <c r="J38" t="n">
-        <v>15.99850988388062</v>
+        <v>12.47077178955078</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>|              ∅              || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               |</t>
+          <t>|  ∅  || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| a,j ||   b,c,d,e,f,g,h,i,k,l,m,n,o   |</t>
         </is>
       </c>
     </row>
@@ -2282,18 +2282,18 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.05460327863693237</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>6.365973472595215</v>
+        <v>3.597303152084351</v>
       </c>
       <c r="J39" t="n">
-        <v>15.99850988388062</v>
+        <v>12.47077178955078</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ |</t>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
+| a ||   b,c,d,e,f,g,h,i,j,k,l,n,o   || m |</t>
         </is>
       </c>
     </row>
@@ -2330,18 +2330,18 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.08183193206787109</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>8.978158473968506</v>
+        <v>7.588261842727661</v>
       </c>
       <c r="J40" t="n">
-        <v>15.99850988388062</v>
+        <v>12.47077178955078</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ || ∅ |</t>
+          <t>|  ∅  || ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
+| a,h || b ||     c,d,e,f,g,i,j,k,l,m,o     || n |</t>
         </is>
       </c>
     </row>
@@ -2378,18 +2378,18 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.1090719699859619</v>
+        <v>0.02679020166397095</v>
       </c>
       <c r="I41" t="n">
-        <v>15.98884868621826</v>
+        <v>11.71812319755554</v>
       </c>
       <c r="J41" t="n">
-        <v>15.99850988388062</v>
+        <v>12.47077178955078</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ || ∅ || ∅ |</t>
+          <t>| ∅ || ∅ || A,B,C,D,E,F,G,I,J,K,L,M,N,O || ∅ || H |
+| a || b ||   c,e,f,g,h,i,j,k,l,m,n,o   || d || ∅ |</t>
         </is>
       </c>
     </row>
@@ -2429,15 +2429,15 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>5.697983264923096</v>
+        <v>1.930575370788574</v>
       </c>
       <c r="J42" t="n">
-        <v>12.68808722496033</v>
+        <v>13.16695261001587</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>|              ∅              || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               |</t>
+          <t>|   ∅   || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| a,e,o ||    b,c,d,f,g,h,i,j,k,l,m,n    |</t>
         </is>
       </c>
     </row>
@@ -2474,18 +2474,18 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.008536279201507568</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>6.250314235687256</v>
+        <v>4.462462186813354</v>
       </c>
       <c r="J43" t="n">
-        <v>12.68808722496033</v>
+        <v>13.16695261001587</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ |</t>
+          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O ||  ∅  || ∅ |
+|    a,b,c,e,g,h,i,j,k,m,n,o    || d,f || l |</t>
         </is>
       </c>
     </row>
@@ -2522,18 +2522,18 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.01283383369445801</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>8.647767543792725</v>
+        <v>8.038507699966431</v>
       </c>
       <c r="J44" t="n">
-        <v>12.68808722496033</v>
+        <v>13.16695261001587</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ || ∅ |</t>
+          <t>| ∅ ||  ∅  || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
+| a || b,n ||     c,d,e,f,g,h,i,k,l,m,o     || j |</t>
         </is>
       </c>
     </row>
@@ -2570,18 +2570,18 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.01714926958084106</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>12.64558911323547</v>
+        <v>11.60323119163513</v>
       </c>
       <c r="J45" t="n">
-        <v>12.68808722496033</v>
+        <v>13.16695261001587</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>|               ∅               || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ || ∅ || ∅ |
-| a,b,c,d,e,f,g,h,i,j,k,l,m,n,o ||               ∅               || ∅ || ∅ || ∅ |</t>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O ||   ∅   || ∅ || ∅ |
+| a ||       b,c,d,h,i,k,l,m,n       || e,g,j || f || o |</t>
         </is>
       </c>
     </row>
